--- a/exports/trend_1d/JINDALSTEL_full_report.xlsx
+++ b/exports/trend_1d/JINDALSTEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>16.2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42083</v>
+        <v>42086</v>
       </c>
       <c r="H2" t="n">
-        <v>164.55</v>
+        <v>154.4</v>
       </c>
       <c r="I2" t="n">
         <v>161.3057470115347</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K2" t="n">
-        <v>8.4</v>
+        <v>1.71</v>
       </c>
       <c r="L2" t="n">
         <v>9.06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.19</v>
+        <v>8.84</v>
       </c>
       <c r="N2" t="n">
         <v>8.640000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>23.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42278</v>
+        <v>42282</v>
       </c>
       <c r="H3" t="n">
-        <v>60.15</v>
+        <v>69.3</v>
       </c>
       <c r="I3" t="n">
         <v>68.90810795102843</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K3" t="n">
-        <v>61.04</v>
+        <v>55.12</v>
       </c>
       <c r="L3" t="n">
         <v>9.84</v>
@@ -612,7 +647,7 @@
         <v>5.82</v>
       </c>
       <c r="N3" t="n">
-        <v>7.26</v>
+        <v>15.21</v>
       </c>
       <c r="O3" t="n">
         <v>-6.17</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>23.29</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H4" t="n">
-        <v>93.45</v>
+        <v>83.95</v>
       </c>
       <c r="I4" t="n">
         <v>85.3872011892971</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="n">
-        <v>34.85</v>
+        <v>21.14</v>
       </c>
       <c r="L4" t="n">
         <v>12.7</v>
@@ -669,7 +716,7 @@
         <v>4.21</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>10.17</v>
       </c>
       <c r="O4" t="n">
         <v>15.21</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>20.09</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42472</v>
+        <v>42473</v>
       </c>
       <c r="H5" t="n">
-        <v>65.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="I5" t="n">
         <v>67.41844286661163</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K5" t="n">
-        <v>22.1</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
         <v>9.59</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>16.34</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42495</v>
+        <v>42496</v>
       </c>
       <c r="H6" t="n">
-        <v>65.95</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>65.30983855044377</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.01</v>
+        <v>-5.66</v>
       </c>
       <c r="L6" t="n">
-        <v>4.41</v>
+        <v>6.18</v>
       </c>
       <c r="M6" t="n">
         <v>1.2</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>19.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42538</v>
+        <v>42541</v>
       </c>
       <c r="H7" t="n">
-        <v>66.3</v>
+        <v>67.45</v>
       </c>
       <c r="I7" t="n">
         <v>67.03965496479894</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.35</v>
+        <v>-5.14</v>
       </c>
       <c r="L7" t="n">
-        <v>5.22</v>
+        <v>6.78</v>
       </c>
       <c r="M7" t="n">
         <v>1.72</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.04</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H8" t="n">
-        <v>81.5</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>76.41802862179688</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K8" t="n">
-        <v>20.83</v>
+        <v>10.67</v>
       </c>
       <c r="L8" t="n">
         <v>10.01</v>
@@ -897,7 +992,7 @@
         <v>3.96</v>
       </c>
       <c r="N8" t="n">
-        <v>6.39</v>
+        <v>8.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.73</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>18.09</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42716</v>
+        <v>42717</v>
       </c>
       <c r="H9" t="n">
-        <v>73.5</v>
+        <v>76.3</v>
       </c>
       <c r="I9" t="n">
         <v>75.99124029003741</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K9" t="n">
-        <v>1.54</v>
+        <v>-2.21</v>
       </c>
       <c r="L9" t="n">
         <v>15.14</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>15.06</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H10" t="n">
-        <v>68.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="I10" t="n">
         <v>66.68157533832931</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.75</v>
+        <v>-14.42</v>
       </c>
       <c r="L10" t="n">
-        <v>12.19</v>
+        <v>14.94</v>
       </c>
       <c r="M10" t="n">
         <v>1.25</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>15.22</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H11" t="n">
-        <v>71.2</v>
+        <v>75.5</v>
       </c>
       <c r="I11" t="n">
         <v>74.52975196095912</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.039999999999999</v>
+        <v>-15.62</v>
       </c>
       <c r="L11" t="n">
-        <v>9.949999999999999</v>
+        <v>17.08</v>
       </c>
       <c r="M11" t="n">
-        <v>0.98</v>
+        <v>1.54</v>
       </c>
       <c r="N11" t="n">
-        <v>2.51</v>
+        <v>6.04</v>
       </c>
       <c r="O11" t="n">
         <v>-4.11</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.85</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42843</v>
+        <v>42844</v>
       </c>
       <c r="H12" t="n">
-        <v>118.55</v>
+        <v>112.55</v>
       </c>
       <c r="I12" t="n">
         <v>116.1270430243845</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12" t="n">
-        <v>57.02</v>
+        <v>49.07</v>
       </c>
       <c r="L12" t="n">
         <v>5.3</v>
@@ -1125,7 +1268,7 @@
         <v>1.56</v>
       </c>
       <c r="N12" t="n">
-        <v>4.58</v>
+        <v>5.06</v>
       </c>
       <c r="O12" t="n">
         <v>6.04</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>17.12</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42880</v>
+        <v>42881</v>
       </c>
       <c r="H13" t="n">
-        <v>118.5</v>
+        <v>125</v>
       </c>
       <c r="I13" t="n">
         <v>123.9373272145217</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.29</v>
+        <v>-11.06</v>
       </c>
       <c r="L13" t="n">
-        <v>6.53</v>
+        <v>11.73</v>
       </c>
       <c r="M13" t="n">
         <v>1.62</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>15.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42950</v>
+        <v>42951</v>
       </c>
       <c r="H14" t="n">
-        <v>142.1</v>
+        <v>138.35</v>
       </c>
       <c r="I14" t="n">
         <v>139.9585523802656</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K14" t="n">
-        <v>13.68</v>
+        <v>10.68</v>
       </c>
       <c r="L14" t="n">
         <v>7.56</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>16.58</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42993</v>
+        <v>42996</v>
       </c>
       <c r="H15" t="n">
-        <v>149.15</v>
+        <v>150.7</v>
       </c>
       <c r="I15" t="n">
         <v>150.6777812330314</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.81</v>
+        <v>-8.93</v>
       </c>
       <c r="L15" t="n">
-        <v>8.890000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="M15" t="n">
         <v>3.02</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.17</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H16" t="n">
-        <v>139.65</v>
+        <v>134.15</v>
       </c>
       <c r="I16" t="n">
         <v>137.6725906994135</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.33</v>
+        <v>-10.98</v>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>12.48</v>
       </c>
       <c r="M16" t="n">
         <v>0.72</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>15.07</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43013</v>
+        <v>43014</v>
       </c>
       <c r="H17" t="n">
-        <v>147.85</v>
+        <v>152.75</v>
       </c>
       <c r="I17" t="n">
         <v>152.6293979410016</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.21</v>
+        <v>-13.87</v>
       </c>
       <c r="L17" t="n">
-        <v>11.03</v>
+        <v>14.61</v>
       </c>
       <c r="M17" t="n">
         <v>1.99</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.97</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43164</v>
+        <v>43165</v>
       </c>
       <c r="H18" t="n">
-        <v>238.05</v>
+        <v>233.65</v>
       </c>
       <c r="I18" t="n">
         <v>236.7141080239503</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K18" t="n">
-        <v>55.84</v>
+        <v>52.96</v>
       </c>
       <c r="L18" t="n">
         <v>3.04</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>20.78</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43202</v>
+        <v>43203</v>
       </c>
       <c r="H19" t="n">
-        <v>243.75</v>
+        <v>251.15</v>
       </c>
       <c r="I19" t="n">
         <v>247.9867378554525</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.32</v>
+        <v>-7.49</v>
       </c>
       <c r="L19" t="n">
-        <v>7.34</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>2.44</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>12.66</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43242</v>
+        <v>43243</v>
       </c>
       <c r="H20" t="n">
-        <v>240.35</v>
+        <v>226.15</v>
       </c>
       <c r="I20" t="n">
         <v>232.3047444939972</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.3</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>6.81</v>
+        <v>10.41</v>
       </c>
       <c r="M20" t="n">
         <v>1.48</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>18.58</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43341</v>
+        <v>43342</v>
       </c>
       <c r="H21" t="n">
-        <v>217.55</v>
+        <v>222.75</v>
       </c>
       <c r="I21" t="n">
         <v>219.2615103635367</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="L21" t="n">
         <v>10.94</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>13.1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H22" t="n">
-        <v>223.6</v>
+        <v>196.35</v>
       </c>
       <c r="I22" t="n">
         <v>203.0078328420603</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>0.38</v>
+        <v>-11.85</v>
       </c>
       <c r="L22" t="n">
-        <v>8.84</v>
+        <v>18.02</v>
       </c>
       <c r="M22" t="n">
         <v>0.74</v>
       </c>
       <c r="N22" t="n">
-        <v>4.83</v>
+        <v>12.19</v>
       </c>
       <c r="O22" t="n">
         <v>2.39</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>28.73</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43515</v>
+        <v>43516</v>
       </c>
       <c r="H23" t="n">
-        <v>141.25</v>
+        <v>149.8</v>
       </c>
       <c r="I23" t="n">
         <v>148.9255487617274</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K23" t="n">
-        <v>28.06</v>
+        <v>23.71</v>
       </c>
       <c r="L23" t="n">
         <v>15.61</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>17.05</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43593</v>
+        <v>43594</v>
       </c>
       <c r="H24" t="n">
-        <v>170.15</v>
+        <v>163.05</v>
       </c>
       <c r="I24" t="n">
         <v>166.1808522527834</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K24" t="n">
-        <v>13.58</v>
+        <v>8.85</v>
       </c>
       <c r="L24" t="n">
         <v>5.44</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>16.74</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43767</v>
+        <v>43768</v>
       </c>
       <c r="H25" t="n">
-        <v>112.65</v>
+        <v>115.2</v>
       </c>
       <c r="I25" t="n">
         <v>112.8585255705726</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K25" t="n">
-        <v>30.91</v>
+        <v>29.35</v>
       </c>
       <c r="L25" t="n">
         <v>5.12</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>15.58</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43811</v>
+        <v>43812</v>
       </c>
       <c r="H26" t="n">
-        <v>142.25</v>
+        <v>138.85</v>
       </c>
       <c r="I26" t="n">
         <v>139.405643575353</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K26" t="n">
-        <v>23.48</v>
+        <v>20.53</v>
       </c>
       <c r="L26" t="n">
         <v>3.52</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>22.65</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43823</v>
+        <v>43825</v>
       </c>
       <c r="H27" t="n">
-        <v>160.05</v>
+        <v>163.55</v>
       </c>
       <c r="I27" t="n">
         <v>162.686836403764</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-15.27</v>
+        <v>-17.79</v>
       </c>
       <c r="L27" t="n">
-        <v>16.67</v>
+        <v>18.69</v>
       </c>
       <c r="M27" t="n">
         <v>1.28</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>14.16</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H28" t="n">
-        <v>179</v>
+        <v>170.15</v>
       </c>
       <c r="I28" t="n">
         <v>172.1343907777738</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K28" t="n">
-        <v>9.449999999999999</v>
+        <v>4.04</v>
       </c>
       <c r="L28" t="n">
         <v>3.06</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.39</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43973</v>
+        <v>43977</v>
       </c>
       <c r="H29" t="n">
-        <v>96.59999999999999</v>
+        <v>109.15</v>
       </c>
       <c r="I29" t="n">
         <v>104.5431805498812</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K29" t="n">
-        <v>43.23</v>
+        <v>35.85</v>
       </c>
       <c r="L29" t="n">
         <v>3.32</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>23.91</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H30" t="n">
-        <v>216.3</v>
+        <v>205.1</v>
       </c>
       <c r="I30" t="n">
         <v>205.5152324086745</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K30" t="n">
-        <v>98.17</v>
+        <v>87.91</v>
       </c>
       <c r="L30" t="n">
         <v>9.210000000000001</v>
@@ -2151,7 +2510,7 @@
         <v>6.91</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="O30" t="n">
         <v>12.99</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>17.21</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44124</v>
+        <v>44125</v>
       </c>
       <c r="H31" t="n">
-        <v>200.45</v>
+        <v>209.1</v>
       </c>
       <c r="I31" t="n">
         <v>202.5811715285769</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K31" t="n">
-        <v>2.27</v>
+        <v>-1.95</v>
       </c>
       <c r="L31" t="n">
         <v>10.19</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>15.54</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H32" t="n">
-        <v>270.95</v>
+        <v>261.75</v>
       </c>
       <c r="I32" t="n">
         <v>261.8368675755177</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>29.58</v>
+        <v>25.18</v>
       </c>
       <c r="L32" t="n">
         <v>11.76</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>19.81</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44237</v>
+        <v>44238</v>
       </c>
       <c r="H33" t="n">
-        <v>311.45</v>
+        <v>315.55</v>
       </c>
       <c r="I33" t="n">
         <v>313.5899190653327</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K33" t="n">
-        <v>-18.99</v>
+        <v>-20.55</v>
       </c>
       <c r="L33" t="n">
         <v>21.64</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>15.09</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44328</v>
+        <v>44330</v>
       </c>
       <c r="H34" t="n">
-        <v>456.6</v>
+        <v>417.3</v>
       </c>
       <c r="I34" t="n">
         <v>434.9631822809035</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K34" t="n">
-        <v>44.7</v>
+        <v>32.25</v>
       </c>
       <c r="L34" t="n">
         <v>5.97</v>
@@ -2379,7 +2786,7 @@
         <v>3.12</v>
       </c>
       <c r="N34" t="n">
-        <v>5.66</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O34" t="n">
         <v>1.32</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>21.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44405</v>
+        <v>44406</v>
       </c>
       <c r="H35" t="n">
-        <v>419.7</v>
+        <v>437.6</v>
       </c>
       <c r="I35" t="n">
         <v>425.978381012933</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.58</v>
+        <v>-4.86</v>
       </c>
       <c r="L35" t="n">
         <v>10.71</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>12.73</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H36" t="n">
-        <v>408</v>
+        <v>376.85</v>
       </c>
       <c r="I36" t="n">
         <v>386.2320237019953</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.76</v>
+        <v>-13.88</v>
       </c>
       <c r="L36" t="n">
-        <v>9.43</v>
+        <v>14.53</v>
       </c>
       <c r="M36" t="n">
-        <v>0.59</v>
+        <v>4.17</v>
       </c>
       <c r="N36" t="n">
-        <v>4.23</v>
+        <v>7.63</v>
       </c>
       <c r="O36" t="n">
         <v>4.26</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>16.4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44469</v>
+        <v>44470</v>
       </c>
       <c r="H37" t="n">
-        <v>389.25</v>
+        <v>401.7</v>
       </c>
       <c r="I37" t="n">
         <v>399.4371954681092</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.29</v>
+        <v>-6.59</v>
       </c>
       <c r="L37" t="n">
-        <v>8.35</v>
+        <v>8.66</v>
       </c>
       <c r="M37" t="n">
         <v>1.8</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.83</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44509</v>
+        <v>44510</v>
       </c>
       <c r="H38" t="n">
-        <v>413.3</v>
+        <v>399.25</v>
       </c>
       <c r="I38" t="n">
         <v>404.4648564296513</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K38" t="n">
-        <v>2.89</v>
+        <v>-0.61</v>
       </c>
       <c r="L38" t="n">
         <v>5.5</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>14.3</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44539</v>
+        <v>44540</v>
       </c>
       <c r="H39" t="n">
-        <v>390.95</v>
+        <v>395.45</v>
       </c>
       <c r="I39" t="n">
         <v>393.5280655313778</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K39" t="n">
-        <v>2.08</v>
+        <v>0.95</v>
       </c>
       <c r="L39" t="n">
         <v>3.34</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.72</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H40" t="n">
-        <v>405.15</v>
+        <v>376.95</v>
       </c>
       <c r="I40" t="n">
         <v>379.9334863423092</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K40" t="n">
-        <v>2.45</v>
+        <v>-4.68</v>
       </c>
       <c r="L40" t="n">
         <v>9.699999999999999</v>
@@ -2721,7 +3200,7 @@
         <v>1.57</v>
       </c>
       <c r="N40" t="n">
-        <v>5.67</v>
+        <v>6.96</v>
       </c>
       <c r="O40" t="n">
         <v>1.15</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>15.49</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44595</v>
+        <v>44596</v>
       </c>
       <c r="H41" t="n">
-        <v>417.5</v>
+        <v>424.4</v>
       </c>
       <c r="I41" t="n">
         <v>417.6929720387812</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.76</v>
+        <v>-12.59</v>
       </c>
       <c r="L41" t="n">
-        <v>12.95</v>
+        <v>14.47</v>
       </c>
       <c r="M41" t="n">
         <v>1.63</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>11.07</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H42" t="n">
-        <v>403</v>
+        <v>369.8</v>
       </c>
       <c r="I42" t="n">
         <v>389.0927526119859</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.04</v>
+        <v>-12.87</v>
       </c>
       <c r="L42" t="n">
-        <v>7.4</v>
+        <v>13.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3.22</v>
+        <v>3.97</v>
       </c>
       <c r="N42" t="n">
-        <v>6.59</v>
+        <v>8.24</v>
       </c>
       <c r="O42" t="n">
         <v>1.65</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>17.86</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44620</v>
+        <v>44622</v>
       </c>
       <c r="H43" t="n">
-        <v>424.85</v>
+        <v>444.15</v>
       </c>
       <c r="I43" t="n">
         <v>435.8498890571084</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K43" t="n">
-        <v>-14.89</v>
+        <v>-20.11</v>
       </c>
       <c r="L43" t="n">
-        <v>15.31</v>
+        <v>22.3</v>
       </c>
       <c r="M43" t="n">
         <v>3.69</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>16.82</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H44" t="n">
-        <v>523.25</v>
+        <v>503.8</v>
       </c>
       <c r="I44" t="n">
         <v>513.3037468409226</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K44" t="n">
-        <v>17.81</v>
+        <v>13.43</v>
       </c>
       <c r="L44" t="n">
         <v>5.27</v>
       </c>
       <c r="M44" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="N44" t="n">
         <v>5.01</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44764</v>
+        <v>44767</v>
       </c>
       <c r="H45" t="n">
-        <v>360.2</v>
+        <v>370.15</v>
       </c>
       <c r="I45" t="n">
         <v>364.2229669601364</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K45" t="n">
-        <v>28.5</v>
+        <v>26.53</v>
       </c>
       <c r="L45" t="n">
         <v>2.42</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.33</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H46" t="n">
-        <v>425.8</v>
+        <v>397.3</v>
       </c>
       <c r="I46" t="n">
         <v>410.2395489493239</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K46" t="n">
-        <v>15.03</v>
+        <v>7.33</v>
       </c>
       <c r="L46" t="n">
         <v>3.49</v>
@@ -3063,7 +3614,7 @@
         <v>2.31</v>
       </c>
       <c r="N46" t="n">
-        <v>5.15</v>
+        <v>6.69</v>
       </c>
       <c r="O46" t="n">
         <v>2.76</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.95</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H47" t="n">
-        <v>439.5</v>
+        <v>453</v>
       </c>
       <c r="I47" t="n">
         <v>444.8367031625385</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>-10.62</v>
+        <v>-14.02</v>
       </c>
       <c r="L47" t="n">
-        <v>10.89</v>
+        <v>14.46</v>
       </c>
       <c r="M47" t="n">
         <v>3.19</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.93</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>539.85</v>
+        <v>524.3</v>
       </c>
       <c r="I48" t="n">
         <v>525.8642067277924</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K48" t="n">
-        <v>19.17</v>
+        <v>15.74</v>
       </c>
       <c r="L48" t="n">
         <v>6.29</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>10.13</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44922</v>
+        <v>44923</v>
       </c>
       <c r="H49" t="n">
-        <v>575.95</v>
+        <v>578.2</v>
       </c>
       <c r="I49" t="n">
         <v>576.5384290481202</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>-9.85</v>
+        <v>-10.28</v>
       </c>
       <c r="L49" t="n">
-        <v>10.37</v>
+        <v>11.38</v>
       </c>
       <c r="M49" t="n">
         <v>1.27</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44960</v>
+        <v>44963</v>
       </c>
       <c r="H50" t="n">
-        <v>582.65</v>
+        <v>556.85</v>
       </c>
       <c r="I50" t="n">
         <v>562.0484521233914</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K50" t="n">
-        <v>0.77</v>
+        <v>-3.69</v>
       </c>
       <c r="L50" t="n">
-        <v>2.29</v>
+        <v>4.06</v>
       </c>
       <c r="M50" t="n">
         <v>1.07</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>13.78</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45044</v>
+        <v>45048</v>
       </c>
       <c r="H51" t="n">
-        <v>582.85</v>
+        <v>592.75</v>
       </c>
       <c r="I51" t="n">
         <v>587.1358247335959</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.67</v>
+        <v>-6.45</v>
       </c>
       <c r="L51" t="n">
         <v>9.34</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.86</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45062</v>
+        <v>45063</v>
       </c>
       <c r="H52" t="n">
-        <v>560.4</v>
+        <v>532.1</v>
       </c>
       <c r="I52" t="n">
         <v>556.5437064105457</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.46</v>
+        <v>-10.23</v>
       </c>
       <c r="L52" t="n">
-        <v>5.79</v>
+        <v>10.54</v>
       </c>
       <c r="M52" t="n">
-        <v>0.79</v>
+        <v>2.21</v>
       </c>
       <c r="N52" t="n">
-        <v>2.55</v>
+        <v>5.05</v>
       </c>
       <c r="O52" t="n">
         <v>1.7</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>10.2</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45093</v>
+        <v>45096</v>
       </c>
       <c r="H53" t="n">
-        <v>544.2</v>
+        <v>574.5</v>
       </c>
       <c r="I53" t="n">
         <v>549.7287743718</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.27</v>
+        <v>-7.97</v>
       </c>
       <c r="L53" t="n">
-        <v>3.34</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>0.92</v>
+        <v>2.54</v>
       </c>
       <c r="N53" t="n">
-        <v>3.04</v>
+        <v>5.57</v>
       </c>
       <c r="O53" t="n">
         <v>-5.05</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H54" t="n">
-        <v>662.4</v>
+        <v>640.15</v>
       </c>
       <c r="I54" t="n">
         <v>659.8050909838297</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K54" t="n">
-        <v>15.3</v>
+        <v>11.43</v>
       </c>
       <c r="L54" t="n">
         <v>2.97</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>10.01</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H55" t="n">
-        <v>636.7</v>
+        <v>648.3</v>
       </c>
       <c r="I55" t="n">
         <v>646.2335319750235</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>0.54</v>
+        <v>-1.27</v>
       </c>
       <c r="L55" t="n">
         <v>3.73</v>
       </c>
       <c r="M55" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="N55" t="n">
         <v>4.24</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.22</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H56" t="n">
-        <v>807.15</v>
+        <v>764.2</v>
       </c>
       <c r="I56" t="n">
         <v>767.6487596882888</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K56" t="n">
-        <v>24.5</v>
+        <v>17.88</v>
       </c>
       <c r="L56" t="n">
         <v>0.89</v>
@@ -3633,7 +4304,7 @@
         <v>2.25</v>
       </c>
       <c r="N56" t="n">
-        <v>4.81</v>
+        <v>5.32</v>
       </c>
       <c r="O56" t="n">
         <v>1.82</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>14.06</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H57" t="n">
-        <v>849.15</v>
+        <v>868.35</v>
       </c>
       <c r="I57" t="n">
         <v>854.5042048916623</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.12</v>
+        <v>-13.63</v>
       </c>
       <c r="L57" t="n">
-        <v>13.54</v>
+        <v>14.3</v>
       </c>
       <c r="M57" t="n">
         <v>2.01</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>10.02</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H58" t="n">
-        <v>1057.45</v>
+        <v>960.15</v>
       </c>
       <c r="I58" t="n">
         <v>983.9131223704229</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K58" t="n">
-        <v>21.78</v>
+        <v>10.57</v>
       </c>
       <c r="L58" t="n">
         <v>1.52</v>
       </c>
       <c r="M58" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="N58" t="n">
-        <v>2.36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O58" t="n">
         <v>2.26</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>14.04</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H59" t="n">
-        <v>966.9</v>
+        <v>1004.65</v>
       </c>
       <c r="I59" t="n">
         <v>995.351585483744</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.7</v>
+        <v>-4.63</v>
       </c>
       <c r="L59" t="n">
         <v>14.25</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.81</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45579</v>
+        <v>45580</v>
       </c>
       <c r="H60" t="n">
-        <v>993.15</v>
+        <v>968.7</v>
       </c>
       <c r="I60" t="n">
         <v>971.0713137620293</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.14</v>
+        <v>-3.58</v>
       </c>
       <c r="L60" t="n">
         <v>3.95</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>12.28</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="H61" t="n">
-        <v>949.1</v>
+        <v>967.2</v>
       </c>
       <c r="I61" t="n">
         <v>959.078250217147</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K61" t="n">
-        <v>2.02</v>
+        <v>0.15</v>
       </c>
       <c r="L61" t="n">
         <v>3.18</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>8.23</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H62" t="n">
-        <v>931.45</v>
+        <v>922.4</v>
       </c>
       <c r="I62" t="n">
         <v>925.4151536344988</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.7</v>
+        <v>-4.63</v>
       </c>
       <c r="L62" t="n">
-        <v>4.17</v>
+        <v>6.22</v>
       </c>
       <c r="M62" t="n">
-        <v>0.58</v>
+        <v>2.62</v>
       </c>
       <c r="N62" t="n">
         <v>2.52</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.95</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="H63" t="n">
-        <v>860.1</v>
+        <v>879.3</v>
       </c>
       <c r="I63" t="n">
         <v>875.7735910210924</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K63" t="n">
-        <v>6.75</v>
+        <v>4.67</v>
       </c>
       <c r="L63" t="n">
         <v>4.3</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>12.39</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H64" t="n">
-        <v>905.2</v>
+        <v>850.1</v>
       </c>
       <c r="I64" t="n">
         <v>851.7419591789314</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K64" t="n">
-        <v>2.95</v>
+        <v>-3.32</v>
       </c>
       <c r="L64" t="n">
         <v>4.2</v>
@@ -4089,7 +4856,7 @@
         <v>1.41</v>
       </c>
       <c r="N64" t="n">
-        <v>2.06</v>
+        <v>6.09</v>
       </c>
       <c r="O64" t="n">
         <v>2.23</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>12.32</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H65" t="n">
-        <v>854.25</v>
+        <v>881.7</v>
       </c>
       <c r="I65" t="n">
         <v>878.4083690818228</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.49</v>
+        <v>-3.72</v>
       </c>
       <c r="L65" t="n">
         <v>6.91</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>12.55</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="H66" t="n">
-        <v>922.6</v>
+        <v>891</v>
       </c>
       <c r="I66" t="n">
         <v>910.6588237137222</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K66" t="n">
-        <v>4.64</v>
+        <v>1.05</v>
       </c>
       <c r="L66" t="n">
         <v>5.46</v>
@@ -4203,7 +4994,7 @@
         <v>2.06</v>
       </c>
       <c r="N66" t="n">
-        <v>3.36</v>
+        <v>3.43</v>
       </c>
       <c r="O66" t="n">
         <v>3.21</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>10.04</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="H67" t="n">
-        <v>951.25</v>
+        <v>968.7</v>
       </c>
       <c r="I67" t="n">
         <v>958.0057773800803</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.76</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>8.92</v>
+        <v>9.98</v>
       </c>
       <c r="M67" t="n">
         <v>2.12</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.9</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="H68" t="n">
-        <v>1007.6</v>
+        <v>996</v>
       </c>
       <c r="I68" t="n">
         <v>996.2492775318119</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K68" t="n">
-        <v>4.02</v>
+        <v>2.82</v>
       </c>
       <c r="L68" t="n">
         <v>4.33</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="H69" t="n">
-        <v>1034.3</v>
+        <v>1073.5</v>
       </c>
       <c r="I69" t="n">
         <v>1070.960082444865</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.85</v>
+        <v>-7.78</v>
       </c>
       <c r="L69" t="n">
-        <v>4.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M69" t="n">
         <v>0.96</v>
       </c>
       <c r="N69" t="n">
-        <v>2.59</v>
+        <v>3.79</v>
       </c>
       <c r="O69" t="n">
         <v>-1.15</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H70" t="n">
-        <v>1017.9</v>
+        <v>1005.8</v>
       </c>
       <c r="I70" t="n">
         <v>1006.380062615772</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K70" t="n">
-        <v>-5.18</v>
+        <v>-6.31</v>
       </c>
       <c r="L70" t="n">
         <v>6.65</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>7.84</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H71" t="n">
-        <v>1021.3</v>
+        <v>1053.8</v>
       </c>
       <c r="I71" t="n">
         <v>1052.088542361622</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.54</v>
+        <v>-4.77</v>
       </c>
       <c r="L71" t="n">
-        <v>3.05</v>
+        <v>5.89</v>
       </c>
       <c r="M71" t="n">
-        <v>0.6</v>
+        <v>2.07</v>
       </c>
       <c r="N71" t="n">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="O71" t="n">
         <v>-1.19</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>6.95</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H72" t="n">
-        <v>1074.7</v>
+        <v>1013.6</v>
       </c>
       <c r="I72" t="n">
         <v>1014.989578712917</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K72" t="n">
-        <v>1.98</v>
+        <v>-3.81</v>
       </c>
       <c r="L72" t="n">
-        <v>1.08</v>
+        <v>4.16</v>
       </c>
       <c r="M72" t="n">
         <v>0.14</v>
       </c>
       <c r="N72" t="n">
-        <v>0.47</v>
+        <v>5.69</v>
       </c>
       <c r="O72" t="n">
         <v>3.18</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>10.84</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H73" t="n">
-        <v>1080.7</v>
+        <v>1119.4</v>
       </c>
       <c r="I73" t="n">
         <v>1089.223847118283</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>-6.62</v>
+        <v>-10.44</v>
       </c>
       <c r="L73" t="n">
-        <v>8.92</v>
+        <v>10.69</v>
       </c>
       <c r="M73" t="n">
         <v>1.02</v>
       </c>
       <c r="N73" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="O73" t="n">
         <v>-5.69</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>10.07</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H74" t="n">
-        <v>1237.8</v>
+        <v>1168.4</v>
       </c>
       <c r="I74" t="n">
         <v>1177.85345689323</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K74" t="n">
-        <v>10.58</v>
+        <v>4.38</v>
       </c>
       <c r="L74" t="n">
         <v>3.66</v>
@@ -4659,7 +5546,7 @@
         <v>3</v>
       </c>
       <c r="N74" t="n">
-        <v>2.65</v>
+        <v>5.61</v>
       </c>
       <c r="O74" t="n">
         <v>3.58</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>11.14</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H75" t="n">
-        <v>1228.3</v>
+        <v>1270</v>
       </c>
       <c r="I75" t="n">
         <v>1245.936917847152</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K75" t="n">
-        <v>-5.13</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>6.94</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M75" t="n">
         <v>2.1</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>12.34</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H76" t="n">
-        <v>1181.3</v>
+        <v>1156.3</v>
       </c>
       <c r="I76" t="n">
         <v>1162.742859108603</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K76" t="n">
-        <v>-6.98</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>8.24</v>
+        <v>9.44</v>
       </c>
       <c r="M76" t="n">
-        <v>0.92</v>
+        <v>1.38</v>
       </c>
       <c r="N76" t="n">
         <v>2.96</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>8.74</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="H77" t="n">
-        <v>1093.7</v>
+        <v>1102.4</v>
       </c>
       <c r="I77" t="n">
         <v>1102.323341934267</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K77" t="n">
-        <v>5.41</v>
+        <v>4.66</v>
       </c>
       <c r="L77" t="n">
         <v>2.21</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>7.03</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H78" t="n">
-        <v>1120.5</v>
+        <v>1095</v>
       </c>
       <c r="I78" t="n">
         <v>1106.251723072254</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K78" t="n">
-        <v>1.64</v>
+        <v>-0.67</v>
       </c>
       <c r="L78" t="n">
         <v>4.03</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>30</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.2</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="11">
@@ -9965,7 +10920,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -9975,7 +10930,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -9985,7 +10940,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.8</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="14">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.36</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12.71</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.86</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>98.17</v>
+        <v>87.91</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.5</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.37</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.81</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.64</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="25">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.66</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="27">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
